--- a/back_end/data/warehouse/에이스용인.xlsx
+++ b/back_end/data/warehouse/에이스용인.xlsx
@@ -16,7 +16,7 @@
     <t xml:space="preserve">현 재 고  현 황</t>
   </si>
   <si>
-    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-05-29</t>
+    <t xml:space="preserve">위탁자 : 8189                                 조회일자 : 2026-06-05</t>
   </si>
   <si>
     <t>수탁품</t>
@@ -58,45 +58,18 @@
     <t>비고</t>
   </si>
   <si>
-    <t xml:space="preserve">SADIA)닭정육  #SIF1</t>
-  </si>
-  <si>
-    <t>26366234</t>
-  </si>
-  <si>
-    <t>12KG</t>
+    <t xml:space="preserve">SWIFT)돈목뼈  #3W</t>
+  </si>
+  <si>
+    <t>26374190</t>
+  </si>
+  <si>
+    <t>15.88KG</t>
   </si>
   <si>
     <t>BOX</t>
   </si>
   <si>
-    <t xml:space="preserve">260105-01980-9087806     -0224-01690</t>
-  </si>
-  <si>
-    <t>MEDUJJ149403</t>
-  </si>
-  <si>
-    <t>SIF1</t>
-  </si>
-  <si>
-    <t>A502</t>
-  </si>
-  <si>
-    <t>통관</t>
-  </si>
-  <si>
-    <t>브라질</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWIFT)돈목뼈  #3W</t>
-  </si>
-  <si>
-    <t>26374190</t>
-  </si>
-  <si>
-    <t>15.88KG</t>
-  </si>
-  <si>
     <t>260430-00017</t>
   </si>
   <si>
@@ -115,10 +88,10 @@
     <t>미국</t>
   </si>
   <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>1,949.96</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>269.96</t>
   </si>
 </sst>
 </file>
@@ -507,21 +480,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <cols>
-    <col min="1" max="1" width="18.86" customWidth="1"/>
+    <col min="1" max="1" width="17.86" customWidth="1"/>
     <col min="2" max="2" width="9.14" customWidth="1"/>
     <col min="3" max="3" width="7.86" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="30.86" customWidth="1"/>
+    <col min="5" max="5" width="11.71" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="13.14" customWidth="1"/>
     <col min="8" max="8" width="7.57" customWidth="1"/>
     <col min="9" max="9" width="9.14" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="7.43" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="9.57" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="15" width="48.43" customWidth="1"/>
+    <col min="13" max="13" width="2.86" customWidth="1"/>
+    <col min="14" max="14" width="5" customWidth="1"/>
+    <col min="15" max="15" width="74.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -681,90 +654,48 @@
       <c t="s" r="F7" s="5">
         <v>21</v>
       </c>
-      <c r="G7" s="5"/>
+      <c t="s" r="G7" s="5">
+        <v>22</v>
+      </c>
       <c t="s" r="H7" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c t="s" r="I7" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" s="6">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="K7" s="7">
-        <v>1680</v>
+        <v>269.95999999999998</v>
       </c>
       <c r="L7" s="8">
-        <v>46679</v>
-      </c>
-      <c t="s" r="M7" s="5">
-        <v>24</v>
-      </c>
+        <v>46443</v>
+      </c>
+      <c r="M7" s="5"/>
       <c t="s" r="N7" s="5">
         <v>25</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c t="s" r="A8" s="5">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c t="s" r="J8" s="10">
         <v>26</v>
       </c>
-      <c t="s" r="B8" s="5">
+      <c t="s" r="K8" s="10">
         <v>27</v>
       </c>
-      <c t="s" r="C8" s="5">
-        <v>28</v>
-      </c>
-      <c t="s" r="D8" s="5">
-        <v>19</v>
-      </c>
-      <c t="s" r="E8" s="5">
-        <v>29</v>
-      </c>
-      <c t="s" r="F8" s="5">
-        <v>30</v>
-      </c>
-      <c t="s" r="G8" s="5">
-        <v>31</v>
-      </c>
-      <c t="s" r="H8" s="5">
-        <v>32</v>
-      </c>
-      <c t="s" r="I8" s="5">
-        <v>33</v>
-      </c>
-      <c r="J8" s="6">
-        <v>17</v>
-      </c>
-      <c r="K8" s="7">
-        <v>269.95999999999998</v>
-      </c>
-      <c r="L8" s="8">
-        <v>46443</v>
-      </c>
-      <c r="M8" s="5"/>
-      <c t="s" r="N8" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c t="s" r="J9" s="10">
-        <v>35</v>
-      </c>
-      <c t="s" r="K9" s="10">
-        <v>36</v>
-      </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="17">
